--- a/data/trans_orig/IP31KM09_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM09_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,74 +720,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>45970</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>40065</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>50040</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>85,58%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>74,59%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>93,16%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>53173</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>51184</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>99,02%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>95,32%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>45309</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>42929</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>45905</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>98,7%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>93,52%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>50287</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>44311</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>54664</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>86,19%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>75,95%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>93,69%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>133</t>
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>103460</t>
+          <t>91279</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>97686</t>
+          <t>84959</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>107764</t>
+          <t>95106</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>95,47%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7745</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3675</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>13650</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>14,42%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>6,84%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>25,41%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>526</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>596</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2515</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2976</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>8058</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>3681</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>14034</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>13,81%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>6,31%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4279</t>
+          <t>4514</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14357</t>
+          <t>14661</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>14,72%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>437575</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>407512</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>448896</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>93,82%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>87,37%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>96,24%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>569</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>415421</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>403863</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>425383</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>91,94%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>89,38%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>94,15%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>472655</t>
+          <t>388643</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>428646</t>
+          <t>376954</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>486487</t>
+          <t>397298</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>888076</t>
+          <t>826219</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>850618</t>
+          <t>791807</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>904039</t>
+          <t>840526</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,33%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>28848</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>17527</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>58911</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>6,18%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>3,76%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>12,63%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>36411</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>26449</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>47969</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8,06%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,85%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>10,62%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>32595</t>
+          <t>36023</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18763</t>
+          <t>27368</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>76604</t>
+          <t>47712</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>69006</t>
+          <t>64871</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>53043</t>
+          <t>50564</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>106464</t>
+          <t>99283</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>625</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>153312</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>146389</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>158503</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>91,98%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>87,82%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>95,09%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>208</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>137366</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>131053</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>140949</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>93,97%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>89,65%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>96,42%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>166369</t>
+          <t>138699</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>158056</t>
+          <t>133144</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>172140</t>
+          <t>142504</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>303734</t>
+          <t>292010</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>294515</t>
+          <t>283772</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>311053</t>
+          <t>298619</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,15%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>13374</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>8183</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>20297</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>8,02%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>4,91%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>12,18%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>8820</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>5237</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>15133</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>6,03%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>3,58%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>10,35%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14770</t>
+          <t>8441</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8999</t>
+          <t>4636</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23083</t>
+          <t>13996</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>23590</t>
+          <t>21815</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16271</t>
+          <t>15206</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32809</t>
+          <t>30053</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>879</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>636857</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>607353</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>650829</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>92,72%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>88,43%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>94,76%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>843</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>605960</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>592939</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>616407</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>92,98%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>90,98%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>94,58%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>879</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>689310</t>
+          <t>572651</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>643635</t>
+          <t>560716</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>704732</t>
+          <t>582171</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,27 +1824,27 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1295270</t>
+          <t>1209508</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1252343</t>
+          <t>1181449</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1313636</t>
+          <t>1227226</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>49967</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>35995</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>79471</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>7,28%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>5,24%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>11,57%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>45757</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>35310</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>58778</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>7,02%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>5,42%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>9,02%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>55423</t>
+          <t>45060</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>40001</t>
+          <t>35540</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>101098</t>
+          <t>56995</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,22 +1937,22 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>101180</t>
+          <t>95027</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>82814</t>
+          <t>77309</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>144107</t>
+          <t>123086</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>914</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
